--- a/artfynd/A 33751-2024 artfynd.xlsx
+++ b/artfynd/A 33751-2024 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114392072</v>
+        <v>114390067</v>
       </c>
       <c r="B2" t="n">
-        <v>57885</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58602</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>667451</v>
+        <v>667475</v>
       </c>
       <c r="R2" t="n">
-        <v>6615976</v>
+        <v>6615906</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
+          <t>2023-04-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
+          <t>2023-04-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marlijn Sterenborg</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,19 +781,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114390067</v>
+        <v>114392072</v>
       </c>
       <c r="B3" t="n">
-        <v>57885</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58602</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -831,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>667475</v>
+        <v>667451</v>
       </c>
       <c r="R3" t="n">
-        <v>6615906</v>
+        <v>6615976</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-04-03</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-04-03</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
+          <t>Marlijn Sterenborg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 33751-2024 artfynd.xlsx
+++ b/artfynd/A 33751-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>ASC0006 Arlanda Fågelinventering 2023</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114390067</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,8 +894,17 @@
           <t>ASC0006 Arlanda Fågelinventering 2023</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114392072</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>